--- a/artfynd/A 62552-2022 artfynd.xlsx
+++ b/artfynd/A 62552-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,9 +789,1026 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137270037</v>
+      </c>
+      <c r="B3" t="n">
+        <v>87522</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>701810</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6359600</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270037</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137273126</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87522</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>701813</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6359660</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273126</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137271194</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87582</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>701816</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6359664</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271194</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137271196</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87582</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>701800</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6359603</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271196</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137271193</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87475</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>701819</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6359658</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271193</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137271197</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87475</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>701796</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6359605</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271197</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137271191</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87559</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>701826</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6359664</v>
+      </c>
+      <c r="S9" t="n">
+        <v>14</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271191</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137271195</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87559</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>701822</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6359651</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271195</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137271198</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87587</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>701765</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6359568</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271198</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62552-2022 artfynd.xlsx
+++ b/artfynd/A 62552-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,48 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137270037</v>
+        <v>137287626</v>
       </c>
       <c r="B3" t="n">
-        <v>87522</v>
+        <v>87535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701810</v>
+        <v>701838</v>
       </c>
       <c r="R3" t="n">
-        <v>6359600</v>
+        <v>6359616</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,24 +886,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270037</t>
+          <t>https://artportalen.se/Sighting/137287626</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137273126</v>
+        <v>137270037</v>
       </c>
       <c r="B4" t="n">
         <v>87522</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701813</v>
+        <v>701810</v>
       </c>
       <c r="R4" t="n">
-        <v>6359660</v>
+        <v>6359600</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,65 +998,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273126</t>
+          <t>https://artportalen.se/Sighting/137270037</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137271194</v>
+        <v>137273126</v>
       </c>
       <c r="B5" t="n">
-        <v>87582</v>
+        <v>87522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>248947</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701816</v>
+        <v>701813</v>
       </c>
       <c r="R5" t="n">
-        <v>6359664</v>
+        <v>6359660</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,62 +1110,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271194</t>
+          <t>https://artportalen.se/Sighting/137273126</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137271196</v>
+        <v>137291130</v>
       </c>
       <c r="B6" t="n">
-        <v>87582</v>
+        <v>87522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>248947</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701800</v>
+        <v>701761</v>
       </c>
       <c r="R6" t="n">
-        <v>6359603</v>
+        <v>6359580</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1192,22 +1195,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,65 +1225,68 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271196</t>
+          <t>https://artportalen.se/Sighting/137291130</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137271193</v>
+        <v>137291131</v>
       </c>
       <c r="B7" t="n">
-        <v>87475</v>
+        <v>87522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701819</v>
+        <v>701811</v>
       </c>
       <c r="R7" t="n">
-        <v>6359658</v>
+        <v>6359565</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,22 +1310,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,27 +1340,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271193</t>
+          <t>https://artportalen.se/Sighting/137291131</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137271197</v>
+        <v>137271194</v>
       </c>
       <c r="B8" t="n">
-        <v>87475</v>
+        <v>87582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701796</v>
+        <v>701816</v>
       </c>
       <c r="R8" t="n">
-        <v>6359605</v>
+        <v>6359664</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,38 +1463,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271197</t>
+          <t>https://artportalen.se/Sighting/137271194</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137271191</v>
+        <v>137271196</v>
       </c>
       <c r="B9" t="n">
-        <v>87559</v>
+        <v>87582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,13 +1504,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701826</v>
+        <v>701800</v>
       </c>
       <c r="R9" t="n">
-        <v>6359664</v>
+        <v>6359603</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,38 +1575,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271191</t>
+          <t>https://artportalen.se/Sighting/137271196</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137271195</v>
+        <v>137271193</v>
       </c>
       <c r="B10" t="n">
-        <v>87559</v>
+        <v>87475</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1610,13 +1616,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701822</v>
+        <v>701819</v>
       </c>
       <c r="R10" t="n">
-        <v>6359651</v>
+        <v>6359658</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,16 +1687,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271195</t>
+          <t>https://artportalen.se/Sighting/137271193</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137271198</v>
+        <v>137271197</v>
       </c>
       <c r="B11" t="n">
-        <v>87587</v>
+        <v>87475</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6052416</v>
+        <v>248956</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fågelträcksspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius subrugulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bidaud &amp; Armada</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1722,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701765</v>
+        <v>701796</v>
       </c>
       <c r="R11" t="n">
-        <v>6359568</v>
+        <v>6359605</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1757,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1767,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,6 +1798,458 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271197</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137291128</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87475</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>701734</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6359637</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291128</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137271191</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87559</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>701826</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6359664</v>
+      </c>
+      <c r="S13" t="n">
+        <v>14</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271191</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137271195</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87559</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>701822</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6359651</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271195</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137271198</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87587</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>701765</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6359568</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137271198</t>
         </is>
@@ -1809,6 +2267,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62552-2022 artfynd.xlsx
+++ b/artfynd/A 62552-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137287626</v>
       </c>
       <c r="B3" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137270037</v>
       </c>
       <c r="B4" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137273126</v>
       </c>
       <c r="B5" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137291130</v>
       </c>
       <c r="B6" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137291131</v>
       </c>
       <c r="B7" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137271194</v>
       </c>
       <c r="B8" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137271196</v>
       </c>
       <c r="B9" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137271193</v>
       </c>
       <c r="B10" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137271197</v>
       </c>
       <c r="B11" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137291128</v>
       </c>
       <c r="B12" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137271191</v>
       </c>
       <c r="B13" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137271195</v>
       </c>
       <c r="B14" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137271198</v>
       </c>
       <c r="B15" t="n">
-        <v>87587</v>
+        <v>87597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62552-2022 artfynd.xlsx
+++ b/artfynd/A 62552-2022 artfynd.xlsx
@@ -791,48 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137287626</v>
+        <v>137270037</v>
       </c>
       <c r="B3" t="n">
-        <v>87545</v>
+        <v>87533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701838</v>
+        <v>701810</v>
       </c>
       <c r="R3" t="n">
-        <v>6359616</v>
+        <v>6359600</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,27 +886,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137287626</t>
+          <t>https://artportalen.se/Sighting/137270037</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137270037</v>
+        <v>137273126</v>
       </c>
       <c r="B4" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701810</v>
+        <v>701813</v>
       </c>
       <c r="R4" t="n">
-        <v>6359600</v>
+        <v>6359660</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,27 +998,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270037</t>
+          <t>https://artportalen.se/Sighting/137273126</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137273126</v>
+        <v>137291130</v>
       </c>
       <c r="B5" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,16 +1044,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701813</v>
+        <v>701761</v>
       </c>
       <c r="R5" t="n">
-        <v>6359660</v>
+        <v>6359580</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1080,22 +1083,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,27 +1113,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273126</t>
+          <t>https://artportalen.se/Sighting/137291130</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137291130</v>
+        <v>137291131</v>
       </c>
       <c r="B6" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701761</v>
+        <v>701811</v>
       </c>
       <c r="R6" t="n">
-        <v>6359580</v>
+        <v>6359565</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,16 +1239,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291130</t>
+          <t>https://artportalen.se/Sighting/137291131</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137291131</v>
+        <v>137287626</v>
       </c>
       <c r="B7" t="n">
-        <v>87532</v>
+        <v>87370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,17 +1279,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701811</v>
+        <v>701838</v>
       </c>
       <c r="R7" t="n">
-        <v>6359565</v>
+        <v>6359616</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,24 +1337,25 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291131</t>
+          <t>https://artportalen.se/Sighting/137287626</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1364,7 @@
         <v>137271194</v>
       </c>
       <c r="B8" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1476,7 @@
         <v>137271196</v>
       </c>
       <c r="B9" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1588,7 @@
         <v>137271193</v>
       </c>
       <c r="B10" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1700,7 @@
         <v>137271197</v>
       </c>
       <c r="B11" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1812,7 @@
         <v>137291128</v>
       </c>
       <c r="B12" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1928,7 @@
         <v>137271191</v>
       </c>
       <c r="B13" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2040,7 @@
         <v>137271195</v>
       </c>
       <c r="B14" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2152,7 @@
         <v>137271198</v>
       </c>
       <c r="B15" t="n">
-        <v>87597</v>
+        <v>87598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62552-2022 artfynd.xlsx
+++ b/artfynd/A 62552-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137270037</v>
       </c>
       <c r="B3" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137273126</v>
       </c>
       <c r="B4" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137291130</v>
       </c>
       <c r="B5" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137291131</v>
       </c>
       <c r="B6" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137287626</v>
       </c>
       <c r="B7" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137271194</v>
       </c>
       <c r="B8" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137271196</v>
       </c>
       <c r="B9" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137271193</v>
       </c>
       <c r="B10" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137271197</v>
       </c>
       <c r="B11" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137291128</v>
       </c>
       <c r="B12" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137271191</v>
       </c>
       <c r="B13" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137271195</v>
       </c>
       <c r="B14" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>137271198</v>
       </c>
       <c r="B15" t="n">
-        <v>87598</v>
+        <v>87601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62552-2022 artfynd.xlsx
+++ b/artfynd/A 62552-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137270037</v>
       </c>
       <c r="B3" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137273126</v>
       </c>
       <c r="B4" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137291130</v>
       </c>
       <c r="B5" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137291131</v>
       </c>
       <c r="B6" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137287626</v>
       </c>
       <c r="B7" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137271194</v>
       </c>
       <c r="B8" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137271196</v>
       </c>
       <c r="B9" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137271193</v>
       </c>
       <c r="B10" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137271197</v>
       </c>
       <c r="B11" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137291128</v>
       </c>
       <c r="B12" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137271191</v>
       </c>
       <c r="B13" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137271195</v>
       </c>
       <c r="B14" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>137271198</v>
       </c>
       <c r="B15" t="n">
-        <v>87601</v>
+        <v>87606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62552-2022 artfynd.xlsx
+++ b/artfynd/A 62552-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137270037</v>
       </c>
       <c r="B3" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137273126</v>
       </c>
       <c r="B4" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137291130</v>
       </c>
       <c r="B5" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137291131</v>
       </c>
       <c r="B6" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137287626</v>
       </c>
       <c r="B7" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137271194</v>
       </c>
       <c r="B8" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137271196</v>
       </c>
       <c r="B9" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137271193</v>
       </c>
       <c r="B10" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137271197</v>
       </c>
       <c r="B11" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137291128</v>
       </c>
       <c r="B12" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137271191</v>
       </c>
       <c r="B13" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137271195</v>
       </c>
       <c r="B14" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>137271198</v>
       </c>
       <c r="B15" t="n">
-        <v>87606</v>
+        <v>87617</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62552-2022 artfynd.xlsx
+++ b/artfynd/A 62552-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137270037</v>
       </c>
       <c r="B3" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137273126</v>
       </c>
       <c r="B4" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137291130</v>
       </c>
       <c r="B5" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137291131</v>
       </c>
       <c r="B6" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137287626</v>
       </c>
       <c r="B7" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137271194</v>
       </c>
       <c r="B8" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137271196</v>
       </c>
       <c r="B9" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137271193</v>
       </c>
       <c r="B10" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137271197</v>
       </c>
       <c r="B11" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137291128</v>
       </c>
       <c r="B12" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137271191</v>
       </c>
       <c r="B13" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137271195</v>
       </c>
       <c r="B14" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>137271198</v>
       </c>
       <c r="B15" t="n">
-        <v>87617</v>
+        <v>87618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62552-2022 artfynd.xlsx
+++ b/artfynd/A 62552-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137270037</v>
       </c>
       <c r="B3" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137273126</v>
       </c>
       <c r="B4" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137291130</v>
       </c>
       <c r="B5" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137291131</v>
       </c>
       <c r="B6" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137287626</v>
       </c>
       <c r="B7" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137271194</v>
       </c>
       <c r="B8" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137271196</v>
       </c>
       <c r="B9" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137271193</v>
       </c>
       <c r="B10" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137271197</v>
       </c>
       <c r="B11" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137291128</v>
       </c>
       <c r="B12" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137271191</v>
       </c>
       <c r="B13" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137271195</v>
       </c>
       <c r="B14" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>137271198</v>
       </c>
       <c r="B15" t="n">
-        <v>87618</v>
+        <v>87621</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62552-2022 artfynd.xlsx
+++ b/artfynd/A 62552-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137270037</v>
       </c>
       <c r="B3" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137273126</v>
       </c>
       <c r="B4" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137291130</v>
       </c>
       <c r="B5" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137291131</v>
       </c>
       <c r="B6" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137287626</v>
       </c>
       <c r="B7" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137271194</v>
       </c>
       <c r="B8" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137271196</v>
       </c>
       <c r="B9" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137271193</v>
       </c>
       <c r="B10" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137271197</v>
       </c>
       <c r="B11" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137291128</v>
       </c>
       <c r="B12" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137271191</v>
       </c>
       <c r="B13" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137271195</v>
       </c>
       <c r="B14" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>137271198</v>
       </c>
       <c r="B15" t="n">
-        <v>87621</v>
+        <v>87625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
